--- a/data/再保最低资本2024Q3-0901.xlsx
+++ b/data/再保最低资本2024Q3-0901.xlsx
@@ -1023,6 +1023,9 @@
       <c r="P10" t="n">
         <v>1135442</v>
       </c>
+      <c r="Q10" t="n">
+        <v>700136.8199999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1339,6 +1342,9 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>47599.44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1373,6 +1379,9 @@
       <c r="P18" t="n">
         <v>9785.879999999999</v>
       </c>
+      <c r="Q18" t="n">
+        <v>531056.28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1905,6 +1914,9 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0</v>
       </c>
     </row>
